--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D3">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>426</v>
